--- a/Data/Y_Capacity_and_Output.xlsx
+++ b/Data/Y_Capacity_and_Output.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\statistical-model\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\统计建模\数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B128B60-1AD4-456C-A5FC-98BCE0E5E042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CACA11-552D-4DC6-8DE4-3A64DD9DB8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="33">
   <si>
     <t>province_code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,6 +78,82 @@
   </si>
   <si>
     <t>NaN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缺失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2016云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2017云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2018云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023云南统计年鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西统计年鉴2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古统计年鉴2024</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -403,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -443,13 +519,19 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>128.46</v>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -460,13 +542,19 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3">
-        <v>129.22999999999999</v>
+        <v>128.46</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -477,13 +565,19 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4">
-        <v>131.44</v>
+        <v>129.22999999999999</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -494,13 +588,19 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5">
-        <v>150.61000000000001</v>
+        <v>131.44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -511,13 +611,19 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
       <c r="E6">
-        <v>259.20999999999998</v>
+        <v>150.61000000000001</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -528,13 +634,19 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7">
-        <v>331.25</v>
+        <v>259.20999999999998</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -545,13 +657,19 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
       </c>
       <c r="E8">
-        <v>415.52</v>
+        <v>331.25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -562,47 +680,65 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
       </c>
       <c r="E9">
-        <v>452.43</v>
+        <v>415.52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
       </c>
       <c r="E10">
-        <v>57.56</v>
+        <v>452.43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
-      <c r="E11">
-        <v>78.349999999999994</v>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -613,13 +749,19 @@
         <v>9</v>
       </c>
       <c r="C12">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
       </c>
       <c r="E12">
-        <v>120.55</v>
+        <v>57.56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -630,13 +772,19 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
       </c>
       <c r="E13">
-        <v>167.6</v>
+        <v>78.349999999999994</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -647,13 +795,19 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14">
-        <v>227.8</v>
+        <v>120.55</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -664,13 +818,19 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15">
-        <v>217.76</v>
+        <v>167.6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -681,16 +841,22 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16">
-        <v>230.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>227.8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -698,16 +864,22 @@
         <v>9</v>
       </c>
       <c r="C17">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
       </c>
       <c r="E17">
-        <v>196.58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217.76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -715,67 +887,91 @@
         <v>9</v>
       </c>
       <c r="C18">
+        <v>2021</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>230.44</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>2022</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19">
+        <v>196.58</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20">
         <v>2023</v>
       </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18">
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20">
         <v>281.92</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19">
-        <v>2016</v>
-      </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19">
-        <v>337.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20">
-        <v>2017</v>
-      </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20">
-        <v>393.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
       </c>
-      <c r="E21">
-        <v>494.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -783,16 +979,22 @@
         <v>12</v>
       </c>
       <c r="C22">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
       </c>
       <c r="E22">
-        <v>567.20000000000005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>337.5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -800,16 +1002,22 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
       </c>
       <c r="E23">
-        <v>574.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>393.7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -817,16 +1025,22 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
       </c>
       <c r="E24">
-        <v>579.21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>494.7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -834,16 +1048,22 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D25" t="s">
         <v>13</v>
       </c>
       <c r="E25">
-        <v>627.77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>567.20000000000005</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -851,16 +1071,22 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
       </c>
       <c r="E26">
-        <v>625.70000000000005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>574.21</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -868,13 +1094,88 @@
         <v>12</v>
       </c>
       <c r="C27">
+        <v>2021</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>579.21</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>2022</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28">
+        <v>627.77</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>2023</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29">
+        <v>625.70000000000005</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
         <v>2024</v>
       </c>
-      <c r="D27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27">
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
         <v>696.7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Y_Capacity_and_Output.xlsx
+++ b/Data/Y_Capacity_and_Output.xlsx
@@ -5,27 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\统计建模\数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\statistical-model\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CACA11-552D-4DC6-8DE4-3A64DD9DB8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A3507B-6A10-42AC-82C9-C156AE28FC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="48">
   <si>
     <t>province_code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,6 +164,64 @@
   <si>
     <t>内蒙古统计年鉴2024</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南统计年鉴2015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015云南统计年鉴</t>
+  </si>
+  <si>
+    <t>云南省2025年国民经济和社会发展统计公报</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云南省2024年国民经济和社会发展统计公报</t>
   </si>
 </sst>
 </file>
@@ -479,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -524,14 +591,14 @@
       <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
+      <c r="E2">
+        <v>100.01</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -731,37 +798,37 @@
       <c r="D11" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
-        <v>13</v>
+      <c r="E11">
+        <v>556.78</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
       </c>
       <c r="E12">
-        <v>57.56</v>
+        <v>617.67999999999995</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,13 +839,13 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
       </c>
       <c r="E13">
-        <v>78.349999999999994</v>
+        <v>57.56</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -795,13 +862,13 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14">
-        <v>120.55</v>
+        <v>78.349999999999994</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -818,13 +885,13 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15">
-        <v>167.6</v>
+        <v>120.55</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -841,13 +908,13 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16">
-        <v>227.8</v>
+        <v>167.6</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -864,13 +931,13 @@
         <v>9</v>
       </c>
       <c r="C17">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
       </c>
       <c r="E17">
-        <v>217.76</v>
+        <v>227.8</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -887,13 +954,13 @@
         <v>9</v>
       </c>
       <c r="C18">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
       </c>
       <c r="E18">
-        <v>230.44</v>
+        <v>217.76</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -910,13 +977,13 @@
         <v>9</v>
       </c>
       <c r="C19">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
       </c>
       <c r="E19">
-        <v>196.58</v>
+        <v>230.44</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -933,13 +1000,13 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
       </c>
       <c r="E20">
-        <v>281.92</v>
+        <v>196.58</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -956,42 +1023,42 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
       </c>
-      <c r="E21" t="s">
-        <v>13</v>
+      <c r="E21">
+        <v>281.92</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
       </c>
-      <c r="E22">
-        <v>337.5</v>
+      <c r="E22" t="s">
+        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1002,19 +1069,19 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
       </c>
       <c r="E23">
-        <v>393.7</v>
+        <v>337.5</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1025,19 +1092,19 @@
         <v>12</v>
       </c>
       <c r="C24">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
       </c>
       <c r="E24">
-        <v>494.7</v>
+        <v>393.7</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1048,19 +1115,19 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D25" t="s">
         <v>13</v>
       </c>
       <c r="E25">
-        <v>567.20000000000005</v>
+        <v>494.7</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1071,19 +1138,19 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
       </c>
       <c r="E26">
-        <v>574.21</v>
+        <v>567.20000000000005</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1094,19 +1161,19 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
       </c>
       <c r="E27">
-        <v>579.21</v>
+        <v>574.21</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1117,19 +1184,19 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
       <c r="E28">
-        <v>627.77</v>
+        <v>579.21</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1140,19 +1207,19 @@
         <v>12</v>
       </c>
       <c r="C29">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
       </c>
       <c r="E29">
-        <v>625.70000000000005</v>
+        <v>627.77</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1163,19 +1230,272 @@
         <v>12</v>
       </c>
       <c r="C30">
+        <v>2023</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>625.70000000000005</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
         <v>2024</v>
       </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30">
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31">
         <v>696.7</v>
       </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32">
+        <v>2015</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32">
+        <v>325.93</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33">
+        <v>2016</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33">
+        <v>314.77999999999997</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34">
+        <v>2017</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34">
+        <v>302.14999999999998</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>2018</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35">
+        <v>236.85</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36">
+        <v>2019</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36">
+        <v>185.75</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37">
+        <v>2020</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37">
+        <v>176.48</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38">
+        <v>2021</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38">
+        <v>169.5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39">
+        <v>2022</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>199.37</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40">
+        <v>2023</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40">
+        <v>195.35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41">
+        <v>2024</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41">
+        <v>197.35</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
